--- a/it_request_forms/006_software_development_quote_request--it_request_forms.xlsx
+++ b/it_request_forms/006_software_development_quote_request--it_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'web_development'}</t>
+          <t>web_development</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Web Development'}</t>
+          <t>Web Development</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'mobile_development'}</t>
+          <t>mobile_development</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Mobile Development'}</t>
+          <t>Mobile Development</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'enterprise_software_development'}</t>
+          <t>enterprise_software_development</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Enterprise Software Development'}</t>
+          <t>Enterprise Software Development</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'full-stack'}</t>
+          <t>full-stack</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Full-Stack'}</t>
+          <t>Full-Stack</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'frontend'}</t>
+          <t>frontend</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Frontend'}</t>
+          <t>Frontend</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'backend'}</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Backend'}</t>
+          <t>Backend</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'database'}</t>
+          <t>database</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Database'}</t>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Chatjimmy'}</t>
+          <t>Chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
